--- a/data/sensors/magnetic-sensors.xlsx
+++ b/data/sensors/magnetic-sensors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\sensors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB2D60-FCA8-4802-859E-DF9AE8665FE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F996A889-6D53-4E82-86FC-A438654C7169}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,9 +342,6 @@
     <t>Operating modes</t>
   </si>
   <si>
-    <t>Direction (axis) of sensitivity</t>
-  </si>
-  <si>
     <t>Bop
 (Gs,25°C)(Gs)</t>
   </si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>Housing</t>
+  </si>
+  <si>
+    <t>Direction</t>
   </si>
 </sst>
 </file>
@@ -705,7 +705,7 @@
     <col min="10" max="10" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -728,22 +728,22 @@
         <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -781,7 +781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -819,7 +819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -857,7 +857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -933,7 +933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -971,7 +971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
